--- a/qoe-evidence-review/data/holdout/kinetic_ridge_pt/financials/monthly_pl.xlsx
+++ b/qoe-evidence-review/data/holdout/kinetic_ridge_pt/financials/monthly_pl.xlsx
@@ -2345,7 +2345,7 @@
         <v>145306.29</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>183306.29</v>
+        <v>183556.29</v>
       </c>
       <c r="AC27" s="4" t="n">
         <v>135906.29</v>
@@ -2354,7 +2354,7 @@
         <v>135906.29</v>
       </c>
       <c r="AE27" s="4" t="n">
-        <v>4076249.45</v>
+        <v>4076499.45</v>
       </c>
     </row>
     <row r="28">
@@ -3437,7 +3437,7 @@
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n">
-        <v>7850</v>
+        <v>46396.51</v>
       </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
@@ -3445,7 +3445,7 @@
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n">
-        <v>7850</v>
+        <v>46396.51</v>
       </c>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
@@ -3455,7 +3455,7 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n">
-        <v>8240</v>
+        <v>47500.46</v>
       </c>
       <c r="S39" s="4" t="n"/>
       <c r="T39" s="4" t="n"/>
@@ -3463,7 +3463,7 @@
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
       <c r="X39" s="4" t="n">
-        <v>34464</v>
+        <v>73724.46000000001</v>
       </c>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n"/>
@@ -3473,10 +3473,10 @@
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n">
-        <v>8600</v>
+        <v>48763.8</v>
       </c>
       <c r="AE39" s="4" t="n">
-        <v>70754</v>
+        <v>266531.74</v>
       </c>
     </row>
     <row r="40">
@@ -4162,7 +4162,7 @@
         <v>826189.71</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>806549.3199999999</v>
+        <v>845095.83</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>784818.84</v>
@@ -4180,7 +4180,7 @@
         <v>789967.89</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>796923.08</v>
+        <v>835469.59</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>814636.11</v>
@@ -4198,7 +4198,7 @@
         <v>856979.41</v>
       </c>
       <c r="R48" s="5" t="n">
-        <v>822094.6</v>
+        <v>861355.0600000001</v>
       </c>
       <c r="S48" s="5" t="n">
         <v>834333.47</v>
@@ -4216,7 +4216,7 @@
         <v>874362.5</v>
       </c>
       <c r="X48" s="5" t="n">
-        <v>921303.25</v>
+        <v>960563.71</v>
       </c>
       <c r="Y48" s="5" t="n">
         <v>820667.79</v>
@@ -4228,16 +4228,16 @@
         <v>906880.4300000001</v>
       </c>
       <c r="AB48" s="5" t="n">
-        <v>938151.39</v>
+        <v>938401.39</v>
       </c>
       <c r="AC48" s="5" t="n">
         <v>878290.08</v>
       </c>
       <c r="AD48" s="5" t="n">
-        <v>853982.9399999999</v>
+        <v>894146.74</v>
       </c>
       <c r="AE48" s="5" t="n">
-        <v>24325657.49</v>
+        <v>24521685.23</v>
       </c>
     </row>
     <row r="49">
@@ -4259,7 +4259,7 @@
         <v>327183.65</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>366282.57</v>
+        <v>327736.06</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>270468.54</v>
@@ -4277,7 +4277,7 @@
         <v>387224.01</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>328428.3</v>
+        <v>289881.79</v>
       </c>
       <c r="M49" s="4" t="n">
         <v>283349.21</v>
@@ -4295,7 +4295,7 @@
         <v>398338.17</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>349460.6</v>
+        <v>310200.14</v>
       </c>
       <c r="S49" s="4" t="n">
         <v>299057.25</v>
@@ -4313,7 +4313,7 @@
         <v>377659.02</v>
       </c>
       <c r="X49" s="4" t="n">
-        <v>239285.47</v>
+        <v>200025.01</v>
       </c>
       <c r="Y49" s="4" t="n">
         <v>292203</v>
@@ -4325,16 +4325,16 @@
         <v>245692.52</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>329989.94</v>
+        <v>329739.94</v>
       </c>
       <c r="AC49" s="4" t="n">
         <v>395312.19</v>
       </c>
       <c r="AD49" s="4" t="n">
-        <v>400945.52</v>
+        <v>360781.72</v>
       </c>
       <c r="AE49" s="4" t="n">
-        <v>8707630.939999999</v>
+        <v>8511603.199999999</v>
       </c>
     </row>
     <row r="50">
@@ -4498,7 +4498,7 @@
         <v>327183.65</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>366282.57</v>
+        <v>327736.06</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>270468.54</v>
@@ -4516,7 +4516,7 @@
         <v>387224.01</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>328428.3</v>
+        <v>289881.79</v>
       </c>
       <c r="M54" s="5" t="n">
         <v>283349.21</v>
@@ -4534,7 +4534,7 @@
         <v>398338.17</v>
       </c>
       <c r="R54" s="5" t="n">
-        <v>349460.6</v>
+        <v>310200.14</v>
       </c>
       <c r="S54" s="5" t="n">
         <v>299057.25</v>
@@ -4552,7 +4552,7 @@
         <v>350059.02</v>
       </c>
       <c r="X54" s="5" t="n">
-        <v>239285.47</v>
+        <v>200025.01</v>
       </c>
       <c r="Y54" s="5" t="n">
         <v>292203</v>
@@ -4564,16 +4564,16 @@
         <v>245692.52</v>
       </c>
       <c r="AB54" s="5" t="n">
-        <v>329989.94</v>
+        <v>329739.94</v>
       </c>
       <c r="AC54" s="5" t="n">
         <v>400212.19</v>
       </c>
       <c r="AD54" s="5" t="n">
-        <v>400945.52</v>
+        <v>360781.72</v>
       </c>
       <c r="AE54" s="5" t="n">
-        <v>8693330.939999999</v>
+        <v>8497303.199999999</v>
       </c>
     </row>
   </sheetData>
